--- a/document/成果ドキュメント_タスク一覧表示画面.xlsx
+++ b/document/成果ドキュメント_タスク一覧表示画面.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCに貼ってある番号\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCに貼ってある番号\Documents\project\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4C2103-1C51-40C2-ACF6-ADFF7FD2265A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9141256-8070-47C5-B04F-03E48A0376B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1430,14 +1430,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="31" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1445,11 +1454,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1460,8 +1469,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1472,37 +1481,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="31" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1520,11 +1517,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1532,23 +1538,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1638,22 +1638,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>251602</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>71886</xdr:rowOff>
+      <xdr:colOff>72809</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>64113</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>539151</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>82205</xdr:rowOff>
+      <xdr:colOff>652801</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>104384</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF18BB65-DB33-C5B7-CA52-5D47C9D654EE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BF4C0F9-FB23-60A3-A381-B1399EF14B1B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1676,8 +1676,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="251602" y="1168160"/>
-          <a:ext cx="7997407" cy="4377441"/>
+          <a:off x="72809" y="1003565"/>
+          <a:ext cx="8252184" cy="4267805"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3138,7 +3138,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="78" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="46"/>
@@ -3173,7 +3173,7 @@
         <v>92</v>
       </c>
       <c r="G2" s="57"/>
-      <c r="H2" s="67">
+      <c r="H2" s="85">
         <v>46121</v>
       </c>
       <c r="I2" s="41" t="s">
@@ -3206,28 +3206,28 @@
       <c r="J4" s="44"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="77"/>
+      <c r="B5" s="71"/>
       <c r="C5" s="55"/>
-      <c r="D5" s="83" t="s">
+      <c r="D5" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="84"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="80" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="61"/>
       <c r="C6" s="62"/>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="73" t="s">
         <v>67</v>
       </c>
       <c r="E6" s="61"/>
@@ -3235,15 +3235,15 @@
       <c r="G6" s="61"/>
       <c r="H6" s="61"/>
       <c r="I6" s="61"/>
-      <c r="J6" s="71"/>
+      <c r="J6" s="74"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="69" t="s">
+      <c r="A7" s="80" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="61"/>
       <c r="C7" s="62"/>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="73" t="s">
         <v>68</v>
       </c>
       <c r="E7" s="61"/>
@@ -3251,15 +3251,15 @@
       <c r="G7" s="61"/>
       <c r="H7" s="61"/>
       <c r="I7" s="61"/>
-      <c r="J7" s="71"/>
+      <c r="J7" s="74"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="80" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="61"/>
       <c r="C8" s="62"/>
-      <c r="D8" s="70" t="s">
+      <c r="D8" s="73" t="s">
         <v>74</v>
       </c>
       <c r="E8" s="61"/>
@@ -3267,17 +3267,17 @@
       <c r="G8" s="61"/>
       <c r="H8" s="61"/>
       <c r="I8" s="61"/>
-      <c r="J8" s="71"/>
+      <c r="J8" s="74"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="84" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="62"/>
-      <c r="D9" s="85" t="s">
+      <c r="D9" s="75" t="s">
         <v>72</v>
       </c>
       <c r="E9" s="61"/>
@@ -3285,15 +3285,15 @@
       <c r="G9" s="61"/>
       <c r="H9" s="61"/>
       <c r="I9" s="61"/>
-      <c r="J9" s="71"/>
+      <c r="J9" s="74"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="79"/>
-      <c r="B10" s="68" t="s">
+      <c r="A10" s="82"/>
+      <c r="B10" s="84" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="62"/>
-      <c r="D10" s="70" t="s">
+      <c r="D10" s="73" t="s">
         <v>70</v>
       </c>
       <c r="E10" s="61"/>
@@ -3301,15 +3301,15 @@
       <c r="G10" s="61"/>
       <c r="H10" s="61"/>
       <c r="I10" s="61"/>
-      <c r="J10" s="71"/>
+      <c r="J10" s="74"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="80"/>
-      <c r="B11" s="68" t="s">
+      <c r="A11" s="83"/>
+      <c r="B11" s="84" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="62"/>
-      <c r="D11" s="85" t="s">
+      <c r="D11" s="75" t="s">
         <v>73</v>
       </c>
       <c r="E11" s="61"/>
@@ -3317,15 +3317,15 @@
       <c r="G11" s="61"/>
       <c r="H11" s="61"/>
       <c r="I11" s="61"/>
-      <c r="J11" s="71"/>
+      <c r="J11" s="74"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="69" t="s">
+      <c r="A12" s="80" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="61"/>
       <c r="C12" s="62"/>
-      <c r="D12" s="70" t="s">
+      <c r="D12" s="73" t="s">
         <v>71</v>
       </c>
       <c r="E12" s="61"/>
@@ -3333,21 +3333,21 @@
       <c r="G12" s="61"/>
       <c r="H12" s="61"/>
       <c r="I12" s="61"/>
-      <c r="J12" s="71"/>
+      <c r="J12" s="74"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="82"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="69"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4338,6 +4338,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4346,25 +4365,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7288,23 +7288,23 @@
       <c r="J4" s="43"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="77"/>
+      <c r="B5" s="71"/>
       <c r="C5" s="55"/>
-      <c r="D5" s="92" t="s">
+      <c r="D5" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="84"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="90" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="61"/>
@@ -7315,19 +7315,19 @@
       <c r="G6" s="61"/>
       <c r="H6" s="61"/>
       <c r="I6" s="61"/>
-      <c r="J6" s="71"/>
+      <c r="J6" s="74"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="93"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="95"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="48"/>
@@ -7339,7 +7339,7 @@
       <c r="G8" s="49"/>
       <c r="H8" s="49"/>
       <c r="I8" s="49"/>
-      <c r="J8" s="96"/>
+      <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="48"/>
@@ -7351,7 +7351,7 @@
       <c r="G9" s="49"/>
       <c r="H9" s="49"/>
       <c r="I9" s="49"/>
-      <c r="J9" s="96"/>
+      <c r="J9" s="95"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="48"/>
@@ -7363,7 +7363,7 @@
       <c r="G10" s="49"/>
       <c r="H10" s="49"/>
       <c r="I10" s="49"/>
-      <c r="J10" s="96"/>
+      <c r="J10" s="95"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="48"/>
@@ -7375,7 +7375,7 @@
       <c r="G11" s="49"/>
       <c r="H11" s="49"/>
       <c r="I11" s="49"/>
-      <c r="J11" s="96"/>
+      <c r="J11" s="95"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="48"/>
@@ -7387,7 +7387,7 @@
       <c r="G12" s="49"/>
       <c r="H12" s="49"/>
       <c r="I12" s="49"/>
-      <c r="J12" s="96"/>
+      <c r="J12" s="95"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="48"/>
@@ -7399,10 +7399,10 @@
       <c r="G13" s="49"/>
       <c r="H13" s="49"/>
       <c r="I13" s="49"/>
-      <c r="J13" s="96"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="89" t="s">
+      <c r="A14" s="90" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="61"/>
@@ -7413,15 +7413,15 @@
       <c r="G14" s="61"/>
       <c r="H14" s="61"/>
       <c r="I14" s="61"/>
-      <c r="J14" s="71"/>
+      <c r="J14" s="74"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="89" t="s">
+      <c r="A15" s="90" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="61"/>
       <c r="C15" s="62"/>
-      <c r="D15" s="70" t="s">
+      <c r="D15" s="73" t="s">
         <v>83</v>
       </c>
       <c r="E15" s="61"/>
@@ -7436,7 +7436,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="89" t="s">
+      <c r="A16" s="90" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="61"/>
@@ -7453,14 +7453,14 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="90" t="s">
+      <c r="H16" s="96" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="61"/>
-      <c r="J16" s="71"/>
+      <c r="J16" s="74"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="88" t="s">
+      <c r="A17" s="87" t="s">
         <v>81</v>
       </c>
       <c r="B17" s="61"/>
@@ -7475,90 +7475,90 @@
       <c r="G17" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="H17" s="70" t="s">
+      <c r="H17" s="73" t="s">
         <v>88</v>
       </c>
       <c r="I17" s="61"/>
-      <c r="J17" s="71"/>
+      <c r="J17" s="74"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="88"/>
+      <c r="A18" s="87"/>
       <c r="B18" s="61"/>
       <c r="C18" s="62"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="70" t="s">
+      <c r="H18" s="73" t="s">
         <v>86</v>
       </c>
       <c r="I18" s="61"/>
-      <c r="J18" s="71"/>
+      <c r="J18" s="74"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="88"/>
+      <c r="A19" s="87"/>
       <c r="B19" s="61"/>
       <c r="C19" s="62"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="70" t="s">
+      <c r="H19" s="73" t="s">
         <v>89</v>
       </c>
       <c r="I19" s="61"/>
-      <c r="J19" s="71"/>
+      <c r="J19" s="74"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="88"/>
+      <c r="A20" s="87"/>
       <c r="B20" s="61"/>
       <c r="C20" s="62"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="70"/>
+      <c r="H20" s="73"/>
       <c r="I20" s="61"/>
-      <c r="J20" s="71"/>
+      <c r="J20" s="74"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="88"/>
+      <c r="A21" s="87"/>
       <c r="B21" s="61"/>
       <c r="C21" s="62"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="73"/>
       <c r="I21" s="61"/>
-      <c r="J21" s="71"/>
+      <c r="J21" s="74"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="88"/>
+      <c r="A22" s="87"/>
       <c r="B22" s="61"/>
       <c r="C22" s="62"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="70"/>
+      <c r="H22" s="73"/>
       <c r="I22" s="61"/>
-      <c r="J22" s="71"/>
+      <c r="J22" s="74"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="87"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="74"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="77"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="82"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="69"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="89" t="s">
+      <c r="A24" s="90" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="61"/>
@@ -7569,15 +7569,15 @@
       <c r="G24" s="61"/>
       <c r="H24" s="61"/>
       <c r="I24" s="61"/>
-      <c r="J24" s="71"/>
+      <c r="J24" s="74"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="89" t="s">
+      <c r="A25" s="90" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="61"/>
       <c r="C25" s="62"/>
-      <c r="D25" s="70" t="s">
+      <c r="D25" s="73" t="s">
         <v>75</v>
       </c>
       <c r="E25" s="61"/>
@@ -7592,7 +7592,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="89" t="s">
+      <c r="A26" s="90" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="61"/>
@@ -7609,14 +7609,14 @@
       <c r="G26" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H26" s="90" t="s">
+      <c r="H26" s="96" t="s">
         <v>18</v>
       </c>
       <c r="I26" s="61"/>
-      <c r="J26" s="71"/>
+      <c r="J26" s="74"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="88" t="s">
+      <c r="A27" s="87" t="s">
         <v>77</v>
       </c>
       <c r="B27" s="61"/>
@@ -7631,83 +7631,83 @@
       <c r="G27" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="H27" s="70" t="s">
+      <c r="H27" s="73" t="s">
         <v>90</v>
       </c>
       <c r="I27" s="61"/>
-      <c r="J27" s="71"/>
+      <c r="J27" s="74"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="88"/>
+      <c r="A28" s="87"/>
       <c r="B28" s="61"/>
       <c r="C28" s="62"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="70"/>
+      <c r="H28" s="73"/>
       <c r="I28" s="61"/>
-      <c r="J28" s="71"/>
+      <c r="J28" s="74"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="88"/>
+      <c r="A29" s="87"/>
       <c r="B29" s="61"/>
       <c r="C29" s="62"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="70"/>
+      <c r="H29" s="73"/>
       <c r="I29" s="61"/>
-      <c r="J29" s="71"/>
+      <c r="J29" s="74"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="88"/>
+      <c r="A30" s="87"/>
       <c r="B30" s="61"/>
       <c r="C30" s="62"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
-      <c r="H30" s="70"/>
+      <c r="H30" s="73"/>
       <c r="I30" s="61"/>
-      <c r="J30" s="71"/>
+      <c r="J30" s="74"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="88"/>
+      <c r="A31" s="87"/>
       <c r="B31" s="61"/>
       <c r="C31" s="62"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="18"/>
       <c r="G31" s="18"/>
-      <c r="H31" s="70"/>
+      <c r="H31" s="73"/>
       <c r="I31" s="61"/>
-      <c r="J31" s="71"/>
+      <c r="J31" s="74"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="88"/>
+      <c r="A32" s="87"/>
       <c r="B32" s="61"/>
       <c r="C32" s="62"/>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="18"/>
       <c r="G32" s="18"/>
-      <c r="H32" s="70"/>
+      <c r="H32" s="73"/>
       <c r="I32" s="61"/>
-      <c r="J32" s="71"/>
+      <c r="J32" s="74"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A33" s="87"/>
-      <c r="B33" s="73"/>
-      <c r="C33" s="74"/>
+      <c r="A33" s="89"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="77"/>
       <c r="D33" s="19"/>
       <c r="E33" s="19"/>
       <c r="F33" s="20"/>
       <c r="G33" s="20"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="73"/>
-      <c r="J33" s="82"/>
+      <c r="H33" s="67"/>
+      <c r="I33" s="68"/>
+      <c r="J33" s="69"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8678,16 +8678,30 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8704,30 +8718,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8747,7 +8747,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="78" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="46"/>
@@ -8758,14 +8758,14 @@
       <c r="G1" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
       <c r="J1" s="55"/>
       <c r="K1" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
       <c r="N1" s="55"/>
       <c r="O1" s="54" t="s">
         <v>6</v>
@@ -8778,7 +8778,7 @@
       <c r="S1" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="84"/>
+      <c r="T1" s="72"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="48"/>
@@ -8788,19 +8788,19 @@
       <c r="E2" s="49"/>
       <c r="F2" s="50"/>
       <c r="G2" s="56"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
       <c r="J2" s="57"/>
       <c r="K2" s="56"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
       <c r="N2" s="57"/>
       <c r="O2" s="56"/>
       <c r="P2" s="57"/>
       <c r="Q2" s="56"/>
       <c r="R2" s="57"/>
       <c r="S2" s="56"/>
-      <c r="T2" s="95"/>
+      <c r="T2" s="94"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="48"/>
@@ -8822,7 +8822,7 @@
       <c r="Q3" s="58"/>
       <c r="R3" s="50"/>
       <c r="S3" s="58"/>
-      <c r="T3" s="96"/>
+      <c r="T3" s="95"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="51"/>
@@ -8844,36 +8844,36 @@
       <c r="Q4" s="59"/>
       <c r="R4" s="53"/>
       <c r="S4" s="59"/>
-      <c r="T4" s="101"/>
+      <c r="T4" s="105"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
       <c r="F5" s="55"/>
-      <c r="G5" s="83" t="s">
+      <c r="G5" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="84"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71"/>
+      <c r="T5" s="72"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="90" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="61"/>
@@ -8881,7 +8881,7 @@
       <c r="D6" s="61"/>
       <c r="E6" s="61"/>
       <c r="F6" s="62"/>
-      <c r="G6" s="70" t="s">
+      <c r="G6" s="73" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="61"/>
@@ -8896,10 +8896,10 @@
       <c r="Q6" s="61"/>
       <c r="R6" s="61"/>
       <c r="S6" s="61"/>
-      <c r="T6" s="71"/>
+      <c r="T6" s="74"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="89" t="s">
+      <c r="A7" s="90" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="61"/>
@@ -8907,7 +8907,7 @@
       <c r="D7" s="61"/>
       <c r="E7" s="61"/>
       <c r="F7" s="62"/>
-      <c r="G7" s="70" t="s">
+      <c r="G7" s="73" t="s">
         <v>37</v>
       </c>
       <c r="H7" s="61"/>
@@ -8922,7 +8922,7 @@
       <c r="Q7" s="61"/>
       <c r="R7" s="61"/>
       <c r="S7" s="61"/>
-      <c r="T7" s="71"/>
+      <c r="T7" s="74"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9121,7 +9121,7 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="89" t="s">
+      <c r="A15" s="90" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="62"/>
@@ -9129,25 +9129,25 @@
         <v>38</v>
       </c>
       <c r="D15" s="62"/>
-      <c r="E15" s="90" t="s">
+      <c r="E15" s="96" t="s">
         <v>45</v>
       </c>
       <c r="F15" s="62"/>
-      <c r="G15" s="90" t="s">
+      <c r="G15" s="96" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="61"/>
       <c r="I15" s="62"/>
-      <c r="J15" s="90" t="s">
+      <c r="J15" s="96" t="s">
         <v>47</v>
       </c>
       <c r="K15" s="62"/>
-      <c r="L15" s="90" t="s">
+      <c r="L15" s="96" t="s">
         <v>48</v>
       </c>
       <c r="M15" s="61"/>
       <c r="N15" s="62"/>
-      <c r="O15" s="90" t="s">
+      <c r="O15" s="96" t="s">
         <v>49</v>
       </c>
       <c r="P15" s="61"/>
@@ -9163,33 +9163,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="102">
+      <c r="A16" s="97">
         <v>1</v>
       </c>
       <c r="B16" s="62"/>
-      <c r="C16" s="103" t="s">
+      <c r="C16" s="98" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="62"/>
-      <c r="E16" s="103" t="s">
+      <c r="E16" s="98" t="s">
         <v>54</v>
       </c>
       <c r="F16" s="62"/>
-      <c r="G16" s="97" t="s">
+      <c r="G16" s="103" t="s">
         <v>55</v>
       </c>
       <c r="H16" s="61"/>
       <c r="I16" s="62"/>
-      <c r="J16" s="97" t="s">
+      <c r="J16" s="103" t="s">
         <v>56</v>
       </c>
       <c r="K16" s="62"/>
-      <c r="L16" s="99" t="s">
+      <c r="L16" s="101" t="s">
         <v>57</v>
       </c>
       <c r="M16" s="61"/>
       <c r="N16" s="62"/>
-      <c r="O16" s="99" t="s">
+      <c r="O16" s="101" t="s">
         <v>58</v>
       </c>
       <c r="P16" s="61"/>
@@ -9205,33 +9205,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="102">
+      <c r="A17" s="97">
         <v>2</v>
       </c>
       <c r="B17" s="62"/>
-      <c r="C17" s="103" t="s">
+      <c r="C17" s="98" t="s">
         <v>59</v>
       </c>
       <c r="D17" s="62"/>
-      <c r="E17" s="103" t="s">
+      <c r="E17" s="98" t="s">
         <v>60</v>
       </c>
       <c r="F17" s="62"/>
-      <c r="G17" s="97" t="s">
+      <c r="G17" s="103" t="s">
         <v>61</v>
       </c>
       <c r="H17" s="61"/>
       <c r="I17" s="62"/>
-      <c r="J17" s="97" t="s">
+      <c r="J17" s="103" t="s">
         <v>62</v>
       </c>
       <c r="K17" s="62"/>
-      <c r="L17" s="99" t="s">
+      <c r="L17" s="101" t="s">
         <v>63</v>
       </c>
       <c r="M17" s="61"/>
       <c r="N17" s="62"/>
-      <c r="O17" s="99" t="s">
+      <c r="O17" s="101" t="s">
         <v>64</v>
       </c>
       <c r="P17" s="61"/>
@@ -9247,21 +9247,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="102"/>
+      <c r="A18" s="97"/>
       <c r="B18" s="62"/>
-      <c r="C18" s="103"/>
+      <c r="C18" s="98"/>
       <c r="D18" s="62"/>
-      <c r="E18" s="103"/>
+      <c r="E18" s="98"/>
       <c r="F18" s="62"/>
-      <c r="G18" s="97"/>
+      <c r="G18" s="103"/>
       <c r="H18" s="61"/>
       <c r="I18" s="62"/>
-      <c r="J18" s="97"/>
+      <c r="J18" s="103"/>
       <c r="K18" s="62"/>
-      <c r="L18" s="99"/>
+      <c r="L18" s="101"/>
       <c r="M18" s="61"/>
       <c r="N18" s="62"/>
-      <c r="O18" s="99"/>
+      <c r="O18" s="101"/>
       <c r="P18" s="61"/>
       <c r="Q18" s="62"/>
       <c r="R18" s="33"/>
@@ -9275,21 +9275,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="102"/>
+      <c r="A19" s="97"/>
       <c r="B19" s="62"/>
-      <c r="C19" s="103"/>
+      <c r="C19" s="98"/>
       <c r="D19" s="62"/>
-      <c r="E19" s="103"/>
+      <c r="E19" s="98"/>
       <c r="F19" s="62"/>
-      <c r="G19" s="97"/>
+      <c r="G19" s="103"/>
       <c r="H19" s="61"/>
       <c r="I19" s="62"/>
-      <c r="J19" s="97"/>
+      <c r="J19" s="103"/>
       <c r="K19" s="62"/>
-      <c r="L19" s="99"/>
+      <c r="L19" s="101"/>
       <c r="M19" s="61"/>
       <c r="N19" s="62"/>
-      <c r="O19" s="99"/>
+      <c r="O19" s="101"/>
       <c r="P19" s="61"/>
       <c r="Q19" s="62"/>
       <c r="R19" s="33"/>
@@ -9303,21 +9303,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="102"/>
+      <c r="A20" s="97"/>
       <c r="B20" s="62"/>
-      <c r="C20" s="103"/>
+      <c r="C20" s="98"/>
       <c r="D20" s="62"/>
-      <c r="E20" s="103"/>
+      <c r="E20" s="98"/>
       <c r="F20" s="62"/>
-      <c r="G20" s="97"/>
+      <c r="G20" s="103"/>
       <c r="H20" s="61"/>
       <c r="I20" s="62"/>
-      <c r="J20" s="97"/>
+      <c r="J20" s="103"/>
       <c r="K20" s="62"/>
-      <c r="L20" s="99"/>
+      <c r="L20" s="101"/>
       <c r="M20" s="61"/>
       <c r="N20" s="62"/>
-      <c r="O20" s="99"/>
+      <c r="O20" s="101"/>
       <c r="P20" s="61"/>
       <c r="Q20" s="62"/>
       <c r="R20" s="33"/>
@@ -9331,21 +9331,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="102"/>
+      <c r="A21" s="97"/>
       <c r="B21" s="62"/>
-      <c r="C21" s="103"/>
+      <c r="C21" s="98"/>
       <c r="D21" s="62"/>
-      <c r="E21" s="103"/>
+      <c r="E21" s="98"/>
       <c r="F21" s="62"/>
-      <c r="G21" s="97"/>
+      <c r="G21" s="103"/>
       <c r="H21" s="61"/>
       <c r="I21" s="62"/>
-      <c r="J21" s="97"/>
+      <c r="J21" s="103"/>
       <c r="K21" s="62"/>
-      <c r="L21" s="99"/>
+      <c r="L21" s="101"/>
       <c r="M21" s="61"/>
       <c r="N21" s="62"/>
-      <c r="O21" s="99"/>
+      <c r="O21" s="101"/>
       <c r="P21" s="61"/>
       <c r="Q21" s="62"/>
       <c r="R21" s="33"/>
@@ -9359,21 +9359,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="102"/>
+      <c r="A22" s="97"/>
       <c r="B22" s="62"/>
-      <c r="C22" s="103"/>
+      <c r="C22" s="98"/>
       <c r="D22" s="62"/>
-      <c r="E22" s="103"/>
+      <c r="E22" s="98"/>
       <c r="F22" s="62"/>
-      <c r="G22" s="97"/>
+      <c r="G22" s="103"/>
       <c r="H22" s="61"/>
       <c r="I22" s="62"/>
-      <c r="J22" s="97"/>
+      <c r="J22" s="103"/>
       <c r="K22" s="62"/>
-      <c r="L22" s="99"/>
+      <c r="L22" s="101"/>
       <c r="M22" s="61"/>
       <c r="N22" s="62"/>
-      <c r="O22" s="99"/>
+      <c r="O22" s="101"/>
       <c r="P22" s="61"/>
       <c r="Q22" s="62"/>
       <c r="R22" s="33"/>
@@ -9387,21 +9387,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="102"/>
+      <c r="A23" s="97"/>
       <c r="B23" s="62"/>
-      <c r="C23" s="103"/>
+      <c r="C23" s="98"/>
       <c r="D23" s="62"/>
-      <c r="E23" s="103"/>
+      <c r="E23" s="98"/>
       <c r="F23" s="62"/>
-      <c r="G23" s="97"/>
+      <c r="G23" s="103"/>
       <c r="H23" s="61"/>
       <c r="I23" s="62"/>
-      <c r="J23" s="97"/>
+      <c r="J23" s="103"/>
       <c r="K23" s="62"/>
-      <c r="L23" s="99"/>
+      <c r="L23" s="101"/>
       <c r="M23" s="61"/>
       <c r="N23" s="62"/>
-      <c r="O23" s="99"/>
+      <c r="O23" s="101"/>
       <c r="P23" s="61"/>
       <c r="Q23" s="62"/>
       <c r="R23" s="33"/>
@@ -9415,21 +9415,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="102"/>
+      <c r="A24" s="97"/>
       <c r="B24" s="62"/>
-      <c r="C24" s="103"/>
+      <c r="C24" s="98"/>
       <c r="D24" s="62"/>
-      <c r="E24" s="103"/>
+      <c r="E24" s="98"/>
       <c r="F24" s="62"/>
-      <c r="G24" s="97"/>
+      <c r="G24" s="103"/>
       <c r="H24" s="61"/>
       <c r="I24" s="62"/>
-      <c r="J24" s="97"/>
+      <c r="J24" s="103"/>
       <c r="K24" s="62"/>
-      <c r="L24" s="99"/>
+      <c r="L24" s="101"/>
       <c r="M24" s="61"/>
       <c r="N24" s="62"/>
-      <c r="O24" s="99"/>
+      <c r="O24" s="101"/>
       <c r="P24" s="61"/>
       <c r="Q24" s="62"/>
       <c r="R24" s="33"/>
@@ -9443,21 +9443,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="102"/>
+      <c r="A25" s="97"/>
       <c r="B25" s="62"/>
-      <c r="C25" s="103"/>
+      <c r="C25" s="98"/>
       <c r="D25" s="62"/>
-      <c r="E25" s="103"/>
+      <c r="E25" s="98"/>
       <c r="F25" s="62"/>
-      <c r="G25" s="97"/>
+      <c r="G25" s="103"/>
       <c r="H25" s="61"/>
       <c r="I25" s="62"/>
-      <c r="J25" s="97"/>
+      <c r="J25" s="103"/>
       <c r="K25" s="62"/>
-      <c r="L25" s="99"/>
+      <c r="L25" s="101"/>
       <c r="M25" s="61"/>
       <c r="N25" s="62"/>
-      <c r="O25" s="99"/>
+      <c r="O25" s="101"/>
       <c r="P25" s="61"/>
       <c r="Q25" s="62"/>
       <c r="R25" s="33"/>
@@ -9471,21 +9471,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="102"/>
+      <c r="A26" s="97"/>
       <c r="B26" s="62"/>
-      <c r="C26" s="103"/>
+      <c r="C26" s="98"/>
       <c r="D26" s="62"/>
-      <c r="E26" s="103"/>
+      <c r="E26" s="98"/>
       <c r="F26" s="62"/>
-      <c r="G26" s="97"/>
+      <c r="G26" s="103"/>
       <c r="H26" s="61"/>
       <c r="I26" s="62"/>
-      <c r="J26" s="97"/>
+      <c r="J26" s="103"/>
       <c r="K26" s="62"/>
-      <c r="L26" s="99"/>
+      <c r="L26" s="101"/>
       <c r="M26" s="61"/>
       <c r="N26" s="62"/>
-      <c r="O26" s="99"/>
+      <c r="O26" s="101"/>
       <c r="P26" s="61"/>
       <c r="Q26" s="62"/>
       <c r="R26" s="33"/>
@@ -9499,21 +9499,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="102"/>
+      <c r="A27" s="97"/>
       <c r="B27" s="62"/>
-      <c r="C27" s="103"/>
+      <c r="C27" s="98"/>
       <c r="D27" s="62"/>
-      <c r="E27" s="103"/>
+      <c r="E27" s="98"/>
       <c r="F27" s="62"/>
-      <c r="G27" s="97"/>
+      <c r="G27" s="103"/>
       <c r="H27" s="61"/>
       <c r="I27" s="62"/>
-      <c r="J27" s="97"/>
+      <c r="J27" s="103"/>
       <c r="K27" s="62"/>
-      <c r="L27" s="99"/>
+      <c r="L27" s="101"/>
       <c r="M27" s="61"/>
       <c r="N27" s="62"/>
-      <c r="O27" s="99"/>
+      <c r="O27" s="101"/>
       <c r="P27" s="61"/>
       <c r="Q27" s="62"/>
       <c r="R27" s="33"/>
@@ -9527,21 +9527,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="102"/>
+      <c r="A28" s="97"/>
       <c r="B28" s="62"/>
-      <c r="C28" s="103"/>
+      <c r="C28" s="98"/>
       <c r="D28" s="62"/>
-      <c r="E28" s="103"/>
+      <c r="E28" s="98"/>
       <c r="F28" s="62"/>
-      <c r="G28" s="97"/>
+      <c r="G28" s="103"/>
       <c r="H28" s="61"/>
       <c r="I28" s="62"/>
-      <c r="J28" s="97"/>
+      <c r="J28" s="103"/>
       <c r="K28" s="62"/>
-      <c r="L28" s="99"/>
+      <c r="L28" s="101"/>
       <c r="M28" s="61"/>
       <c r="N28" s="62"/>
-      <c r="O28" s="99"/>
+      <c r="O28" s="101"/>
       <c r="P28" s="61"/>
       <c r="Q28" s="62"/>
       <c r="R28" s="33"/>
@@ -9555,21 +9555,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="102"/>
+      <c r="A29" s="97"/>
       <c r="B29" s="62"/>
-      <c r="C29" s="103"/>
+      <c r="C29" s="98"/>
       <c r="D29" s="62"/>
-      <c r="E29" s="103"/>
+      <c r="E29" s="98"/>
       <c r="F29" s="62"/>
-      <c r="G29" s="97"/>
+      <c r="G29" s="103"/>
       <c r="H29" s="61"/>
       <c r="I29" s="62"/>
-      <c r="J29" s="97"/>
+      <c r="J29" s="103"/>
       <c r="K29" s="62"/>
-      <c r="L29" s="99"/>
+      <c r="L29" s="101"/>
       <c r="M29" s="61"/>
       <c r="N29" s="62"/>
-      <c r="O29" s="99"/>
+      <c r="O29" s="101"/>
       <c r="P29" s="61"/>
       <c r="Q29" s="62"/>
       <c r="R29" s="33"/>
@@ -9583,21 +9583,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="102"/>
+      <c r="A30" s="97"/>
       <c r="B30" s="62"/>
-      <c r="C30" s="103"/>
+      <c r="C30" s="98"/>
       <c r="D30" s="62"/>
-      <c r="E30" s="103"/>
+      <c r="E30" s="98"/>
       <c r="F30" s="62"/>
-      <c r="G30" s="97"/>
+      <c r="G30" s="103"/>
       <c r="H30" s="61"/>
       <c r="I30" s="62"/>
-      <c r="J30" s="97"/>
+      <c r="J30" s="103"/>
       <c r="K30" s="62"/>
-      <c r="L30" s="99"/>
+      <c r="L30" s="101"/>
       <c r="M30" s="61"/>
       <c r="N30" s="62"/>
-      <c r="O30" s="99"/>
+      <c r="O30" s="101"/>
       <c r="P30" s="61"/>
       <c r="Q30" s="62"/>
       <c r="R30" s="33"/>
@@ -9611,23 +9611,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="105"/>
-      <c r="B31" s="74"/>
-      <c r="C31" s="106"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="98"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="98"/>
-      <c r="K31" s="74"/>
-      <c r="L31" s="100"/>
-      <c r="M31" s="73"/>
-      <c r="N31" s="74"/>
-      <c r="O31" s="100"/>
-      <c r="P31" s="73"/>
-      <c r="Q31" s="74"/>
+      <c r="A31" s="99"/>
+      <c r="B31" s="77"/>
+      <c r="C31" s="100"/>
+      <c r="D31" s="77"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="106"/>
+      <c r="H31" s="68"/>
+      <c r="I31" s="77"/>
+      <c r="J31" s="106"/>
+      <c r="K31" s="77"/>
+      <c r="L31" s="102"/>
+      <c r="M31" s="68"/>
+      <c r="N31" s="77"/>
+      <c r="O31" s="102"/>
+      <c r="P31" s="68"/>
+      <c r="Q31" s="77"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10625,6 +10625,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -10649,118 +10761,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
